--- a/artfynd/A 21612-2026 artfynd.xlsx
+++ b/artfynd/A 21612-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,38 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133472137</v>
+        <v>133472407</v>
       </c>
       <c r="B2" t="n">
-        <v>58136</v>
+        <v>96783</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587026</v>
+        <v>587068</v>
       </c>
       <c r="R2" t="n">
-        <v>6373851</v>
+        <v>6373792</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133477595</v>
+        <v>133473367</v>
       </c>
       <c r="B3" t="n">
-        <v>92370</v>
+        <v>96783</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,37 +802,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jungfruängen, Jungfruängen, Sm</t>
+          <t>Kalmarehagen, Kalmarehagen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587115</v>
+        <v>587226</v>
       </c>
       <c r="R3" t="n">
-        <v>6373900</v>
+        <v>6373709</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133475431</v>
+        <v>133474240</v>
       </c>
       <c r="B4" t="n">
-        <v>96768</v>
+        <v>96783</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,29 +935,20 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skrabbhagen, Skrabbhagen, Sm</t>
+          <t>Kalmarehagen, Kalmarehagen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587451</v>
+        <v>587371</v>
       </c>
       <c r="R4" t="n">
-        <v>6373682</v>
+        <v>6373696</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133471790</v>
+        <v>133475431</v>
       </c>
       <c r="B5" t="n">
-        <v>57162</v>
+        <v>96783</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,42 +1025,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jungfruängen, Jungfruängen, Sm</t>
+          <t>Skrabbhagen, Skrabbhagen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586993</v>
+        <v>587451</v>
       </c>
       <c r="R5" t="n">
-        <v>6373884</v>
+        <v>6373682</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133474240</v>
+        <v>133537472</v>
       </c>
       <c r="B6" t="n">
-        <v>96768</v>
+        <v>96783</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,19 +1159,23 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kalmarehagen, Kalmarehagen, Sm</t>
+          <t>Ramnebo, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587371</v>
+        <v>586991</v>
       </c>
       <c r="R6" t="n">
-        <v>6373696</v>
+        <v>6373778</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1187,22 +1199,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1211,75 +1223,76 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Ante Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Ante Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133473367</v>
+        <v>133474944</v>
       </c>
       <c r="B7" t="n">
-        <v>96768</v>
+        <v>93271</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kalmarehagen, Kalmarehagen, Sm</t>
+          <t>Skrabbhagen, Skrabbhagen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587226</v>
+        <v>587451</v>
       </c>
       <c r="R7" t="n">
-        <v>6373709</v>
+        <v>6373682</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1308,7 +1321,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1318,7 +1331,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,50 +1358,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133472844</v>
+        <v>133477109</v>
       </c>
       <c r="B8" t="n">
-        <v>57162</v>
+        <v>93271</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jungfruängen, Jungfruängen, Sm</t>
+          <t>Ramnebo Gatgöl, Ramnebo Gatgöl, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587156</v>
+        <v>587227</v>
       </c>
       <c r="R8" t="n">
-        <v>6373777</v>
+        <v>6373809</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1420,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1430,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,44 +1474,35 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133477641</v>
+        <v>133477595</v>
       </c>
       <c r="B9" t="n">
-        <v>91980</v>
+        <v>92385</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Jungfruängen, Jungfruängen, Sm</t>
@@ -1536,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1546,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1573,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133477551</v>
+        <v>133473064</v>
       </c>
       <c r="B10" t="n">
-        <v>91980</v>
+        <v>91995</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,26 +1609,17 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Jungfruängen, Jungfruängen, Sm</t>
+          <t>Kalmarehagen, Kalmarehagen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587115</v>
+        <v>587190</v>
       </c>
       <c r="R10" t="n">
-        <v>6373893</v>
+        <v>6373761</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1652,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1662,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133472916</v>
+        <v>133476920</v>
       </c>
       <c r="B11" t="n">
-        <v>58136</v>
+        <v>91995</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1700,46 +1699,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Jungfruängen, Jungfruängen, Sm</t>
+          <t>Kalmarehagen, Kalmarehagen, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587168</v>
+        <v>587306</v>
       </c>
       <c r="R11" t="n">
-        <v>6373780</v>
+        <v>6373704</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1768,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,43 +1795,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133479929</v>
+        <v>133477551</v>
       </c>
       <c r="B12" t="n">
-        <v>57162</v>
+        <v>91995</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1850,13 +1839,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587112</v>
+        <v>587115</v>
       </c>
       <c r="R12" t="n">
-        <v>6373853</v>
+        <v>6373893</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1885,7 +1874,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,7 +1884,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,10 +1911,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133476920</v>
+        <v>133477641</v>
       </c>
       <c r="B13" t="n">
-        <v>91980</v>
+        <v>91995</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1950,20 +1939,29 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kalmarehagen, Kalmarehagen, Sm</t>
+          <t>Jungfruängen, Jungfruängen, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587306</v>
+        <v>587115</v>
       </c>
       <c r="R13" t="n">
-        <v>6373704</v>
+        <v>6373900</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1992,7 +1990,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +2000,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,53 +2027,59 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133477749</v>
+        <v>133537484</v>
       </c>
       <c r="B14" t="n">
-        <v>57162</v>
+        <v>91995</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ramnebo Gatgöl, Ramnebo Gatgöl, Sm</t>
+          <t>Ramnebo, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>587152</v>
+        <v>586995</v>
       </c>
       <c r="R14" t="n">
-        <v>6373902</v>
+        <v>6373757</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2099,27 +2103,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Sandbad?</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2128,28 +2127,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Ante Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Ante Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133472407</v>
+        <v>133472246</v>
       </c>
       <c r="B15" t="n">
-        <v>96768</v>
+        <v>57972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2157,31 +2157,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2190,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>587068</v>
+        <v>587043</v>
       </c>
       <c r="R15" t="n">
-        <v>6373792</v>
+        <v>6373808</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
@@ -2225,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2235,7 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2262,10 +2258,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133474944</v>
+        <v>133474318</v>
       </c>
       <c r="B16" t="n">
-        <v>93256</v>
+        <v>57972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,46 +2269,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skrabbhagen, Skrabbhagen, Sm</t>
+          <t>Kalmarehagen, Kalmarehagen, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587451</v>
+        <v>587393</v>
       </c>
       <c r="R16" t="n">
-        <v>6373682</v>
+        <v>6373654</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2341,7 +2328,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2351,7 +2338,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2378,38 +2365,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133472246</v>
+        <v>133471790</v>
       </c>
       <c r="B17" t="n">
-        <v>57972</v>
+        <v>57162</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2418,13 +2405,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587043</v>
+        <v>586993</v>
       </c>
       <c r="R17" t="n">
-        <v>6373808</v>
+        <v>6373884</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2453,7 +2440,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2463,7 +2450,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2490,7 +2477,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133474359</v>
+        <v>133472286</v>
       </c>
       <c r="B18" t="n">
         <v>57162</v>
@@ -2519,19 +2506,24 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skrabbhagen, Skrabbhagen, Sm</t>
+          <t>Jungfruängen, Jungfruängen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587407</v>
+        <v>587043</v>
       </c>
       <c r="R18" t="n">
-        <v>6373661</v>
+        <v>6373808</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2560,7 +2552,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2570,7 +2562,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2597,45 +2589,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133473064</v>
+        <v>133472844</v>
       </c>
       <c r="B19" t="n">
-        <v>91980</v>
+        <v>57162</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kalmarehagen, Kalmarehagen, Sm</t>
+          <t>Jungfruängen, Jungfruängen, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587190</v>
+        <v>587156</v>
       </c>
       <c r="R19" t="n">
-        <v>6373761</v>
+        <v>6373777</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2667,7 +2664,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2677,7 +2674,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2704,7 +2701,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133476774</v>
+        <v>133474359</v>
       </c>
       <c r="B20" t="n">
         <v>57162</v>
@@ -2733,21 +2730,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skrabbhagen, Skrabbhagen, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>587384</v>
+        <v>587407</v>
       </c>
       <c r="R20" t="n">
-        <v>6373702</v>
+        <v>6373661</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2779,7 +2771,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2789,7 +2781,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2928,38 +2920,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133475458</v>
+        <v>133476774</v>
       </c>
       <c r="B22" t="n">
-        <v>58136</v>
+        <v>57162</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2968,13 +2960,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587556</v>
+        <v>587384</v>
       </c>
       <c r="R22" t="n">
-        <v>6373669</v>
+        <v>6373702</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3003,7 +2995,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3013,7 +3005,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3040,10 +3032,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133477109</v>
+        <v>133477749</v>
       </c>
       <c r="B23" t="n">
-        <v>93256</v>
+        <v>57162</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3051,31 +3043,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3084,10 +3072,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587227</v>
+        <v>587152</v>
       </c>
       <c r="R23" t="n">
-        <v>6373809</v>
+        <v>6373902</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3119,7 +3107,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3129,7 +3117,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Sandbad?</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3156,48 +3149,58 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133474318</v>
+        <v>133479929</v>
       </c>
       <c r="B24" t="n">
-        <v>57972</v>
+        <v>57162</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kalmarehagen, Kalmarehagen, Sm</t>
+          <t>Jungfruängen, Jungfruängen, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587393</v>
+        <v>587112</v>
       </c>
       <c r="R24" t="n">
-        <v>6373654</v>
+        <v>6373853</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3226,7 +3229,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3236,7 +3239,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3263,7 +3266,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133472286</v>
+        <v>133537533</v>
       </c>
       <c r="B25" t="n">
         <v>57162</v>
@@ -3291,25 +3294,36 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>färsk spillning</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Jungfruängen, Jungfruängen, Sm</t>
+          <t>Ramnebo, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587043</v>
+        <v>587002</v>
       </c>
       <c r="R25" t="n">
-        <v>6373808</v>
+        <v>6373747</v>
       </c>
       <c r="S25" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3333,22 +3347,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3363,76 +3377,65 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Ante Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Ante Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133537533</v>
+        <v>133472137</v>
       </c>
       <c r="B26" t="n">
-        <v>57162</v>
+        <v>58136</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ramnebo, Sm</t>
+          <t>Jungfruängen, Jungfruängen, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587002</v>
+        <v>587026</v>
       </c>
       <c r="R26" t="n">
-        <v>6373747</v>
+        <v>6373851</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3456,22 +3459,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3486,22 +3489,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133537484</v>
+        <v>133472916</v>
       </c>
       <c r="B27" t="n">
-        <v>91981</v>
+        <v>58136</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3509,48 +3512,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ramnebo, Sm</t>
+          <t>Jungfruängen, Jungfruängen, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586995</v>
+        <v>587168</v>
       </c>
       <c r="R27" t="n">
-        <v>6373757</v>
+        <v>6373780</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3574,22 +3575,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3598,71 +3599,71 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133537472</v>
+        <v>133475458</v>
       </c>
       <c r="B28" t="n">
-        <v>96769</v>
+        <v>58136</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ramnebo, Sm</t>
+          <t>Skrabbhagen, Skrabbhagen, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586991</v>
+        <v>587556</v>
       </c>
       <c r="R28" t="n">
-        <v>6373778</v>
+        <v>6373669</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3686,22 +3687,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3710,22 +3711,128 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>133472576</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Jungfruängen, Jungfruängen, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>587102</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6373799</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21612-2026 artfynd.xlsx
+++ b/artfynd/A 21612-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133472407</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133473367</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133474240</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1127,6 +1147,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133475431</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1239,6 +1264,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133537472</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1355,6 +1385,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133474944</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1471,6 +1506,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133477109</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1578,6 +1618,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133477595</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1685,6 +1730,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133473064</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1792,6 +1842,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133476920</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1908,6 +1963,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133477551</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2024,6 +2084,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133477641</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2143,6 +2208,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133537484</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2255,6 +2325,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133472246</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2362,6 +2437,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133474318</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2474,6 +2554,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133471790</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2586,6 +2671,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133472286</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2698,6 +2788,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133472844</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2805,6 +2900,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133474359</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2917,6 +3017,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133474811</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3029,6 +3134,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133476774</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3146,6 +3256,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133477749</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3263,6 +3378,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133479929</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3386,6 +3506,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133537533</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3498,6 +3623,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133472137</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3614,6 +3744,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133472916</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3726,6 +3861,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133475458</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3833,8 +3973,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133472576</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 21612-2026 artfynd.xlsx
+++ b/artfynd/A 21612-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ29"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,57 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133472407</v>
+        <v>136274000</v>
       </c>
       <c r="B2" t="n">
-        <v>96783</v>
+        <v>79111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Jungfruängen, Jungfruängen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587068</v>
+        <v>587171</v>
       </c>
       <c r="R2" t="n">
-        <v>6373792</v>
+        <v>6373896</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,24 +765,24 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133472407</t>
+          <t>https://artportalen.se/Sighting/136274000</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133473367</v>
+        <v>133472407</v>
       </c>
       <c r="B3" t="n">
         <v>96783</v>
@@ -831,27 +812,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kalmarehagen, Kalmarehagen, Sm</t>
+          <t>Jungfruängen, Jungfruängen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587226</v>
+        <v>587068</v>
       </c>
       <c r="R3" t="n">
-        <v>6373709</v>
+        <v>6373792</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,13 +897,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133473367</t>
+          <t>https://artportalen.se/Sighting/133472407</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133474240</v>
+        <v>133473367</v>
       </c>
       <c r="B4" t="n">
         <v>96783</v>
@@ -950,20 +931,29 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kalmarehagen, Kalmarehagen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587371</v>
+        <v>587226</v>
       </c>
       <c r="R4" t="n">
-        <v>6373696</v>
+        <v>6373709</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,13 +1018,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133474240</t>
+          <t>https://artportalen.se/Sighting/133473367</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133475431</v>
+        <v>133474240</v>
       </c>
       <c r="B5" t="n">
         <v>96783</v>
@@ -1062,29 +1052,20 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skrabbhagen, Skrabbhagen, Sm</t>
+          <t>Kalmarehagen, Kalmarehagen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587451</v>
+        <v>587371</v>
       </c>
       <c r="R5" t="n">
-        <v>6373682</v>
+        <v>6373696</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,7 +1094,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1104,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,13 +1130,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133475431</t>
+          <t>https://artportalen.se/Sighting/133474240</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133537472</v>
+        <v>133475431</v>
       </c>
       <c r="B6" t="n">
         <v>96783</v>
@@ -1183,24 +1164,29 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ramnebo, Sm</t>
+          <t>Skrabbhagen, Skrabbhagen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586991</v>
+        <v>587451</v>
       </c>
       <c r="R6" t="n">
-        <v>6373778</v>
+        <v>6373682</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,22 +1210,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,81 +1234,75 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133537472</t>
+          <t>https://artportalen.se/Sighting/133475431</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133474944</v>
+        <v>133537472</v>
       </c>
       <c r="B7" t="n">
-        <v>93271</v>
+        <v>96783</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skrabbhagen, Skrabbhagen, Sm</t>
+          <t>Ramnebo, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587451</v>
+        <v>586991</v>
       </c>
       <c r="R7" t="n">
-        <v>6373682</v>
+        <v>6373778</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1346,22 +1326,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,80 +1350,72 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Ante Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Ante Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133474944</t>
+          <t>https://artportalen.se/Sighting/133537472</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133477109</v>
+        <v>136274843</v>
       </c>
       <c r="B8" t="n">
-        <v>93271</v>
+        <v>96881</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ramnebo Gatgöl, Ramnebo Gatgöl, Sm</t>
+          <t>Jungfruängen, Jungfruängen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587227</v>
+        <v>587333</v>
       </c>
       <c r="R8" t="n">
-        <v>6373809</v>
+        <v>6373759</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1467,22 +1439,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:14</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:14</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,27 +1459,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133477109</t>
+          <t>https://artportalen.se/Sighting/136274843</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133477595</v>
+        <v>136281124</v>
       </c>
       <c r="B9" t="n">
-        <v>92385</v>
+        <v>96881</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1525,37 +1487,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5420</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Jungfruängen, Jungfruängen, Sm</t>
+          <t>Ramnebo Gatgöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587115</v>
+        <v>587364</v>
       </c>
       <c r="R9" t="n">
-        <v>6373900</v>
+        <v>6373676</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1579,22 +1545,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,71 +1569,76 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133477595</t>
+          <t>https://artportalen.se/Sighting/136281124</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133473064</v>
+        <v>136281338</v>
       </c>
       <c r="B10" t="n">
-        <v>91995</v>
+        <v>96881</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kalmarehagen, Kalmarehagen, Sm</t>
+          <t>Ramnebo Gatgöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587190</v>
+        <v>587226</v>
       </c>
       <c r="R10" t="n">
-        <v>6373761</v>
+        <v>6373705</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1691,22 +1662,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,33 +1686,34 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133473064</t>
+          <t>https://artportalen.se/Sighting/136281338</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133476920</v>
+        <v>133474944</v>
       </c>
       <c r="B11" t="n">
-        <v>91995</v>
+        <v>93271</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,37 +1721,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kalmarehagen, Kalmarehagen, Sm</t>
+          <t>Skrabbhagen, Skrabbhagen, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587306</v>
+        <v>587451</v>
       </c>
       <c r="R11" t="n">
-        <v>6373704</v>
+        <v>6373682</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1808,7 +1789,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1818,7 +1799,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1844,16 +1825,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133476920</t>
+          <t>https://artportalen.se/Sighting/133474944</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133477551</v>
+        <v>133477109</v>
       </c>
       <c r="B12" t="n">
-        <v>91995</v>
+        <v>93271</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,26 +1842,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1890,14 +1871,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Jungfruängen, Jungfruängen, Sm</t>
+          <t>Ramnebo Gatgöl, Ramnebo Gatgöl, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587115</v>
+        <v>587227</v>
       </c>
       <c r="R12" t="n">
-        <v>6373893</v>
+        <v>6373809</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1929,7 +1910,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1939,7 +1920,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1965,50 +1946,41 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133477551</t>
+          <t>https://artportalen.se/Sighting/133477109</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133477641</v>
+        <v>133477595</v>
       </c>
       <c r="B13" t="n">
-        <v>91995</v>
+        <v>92385</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Jungfruängen, Jungfruängen, Sm</t>
@@ -2050,7 +2022,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2060,7 +2032,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2086,13 +2058,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133477641</t>
+          <t>https://artportalen.se/Sighting/133477595</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133537484</v>
+        <v>133473064</v>
       </c>
       <c r="B14" t="n">
         <v>91995</v>
@@ -2120,31 +2092,20 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ramnebo, Sm</t>
+          <t>Kalmarehagen, Kalmarehagen, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586995</v>
+        <v>587190</v>
       </c>
       <c r="R14" t="n">
-        <v>6373757</v>
+        <v>6373761</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2168,22 +2129,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,74 +2153,68 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133537484</t>
+          <t>https://artportalen.se/Sighting/133473064</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133472246</v>
+        <v>133476920</v>
       </c>
       <c r="B15" t="n">
-        <v>57972</v>
+        <v>91995</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Jungfruängen, Jungfruängen, Sm</t>
+          <t>Kalmarehagen, Kalmarehagen, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>587043</v>
+        <v>587306</v>
       </c>
       <c r="R15" t="n">
-        <v>6373808</v>
+        <v>6373704</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
@@ -2291,7 +2246,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2301,7 +2256,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2327,54 +2282,63 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133472246</t>
+          <t>https://artportalen.se/Sighting/133476920</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133474318</v>
+        <v>133477551</v>
       </c>
       <c r="B16" t="n">
-        <v>57972</v>
+        <v>91995</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kalmarehagen, Kalmarehagen, Sm</t>
+          <t>Jungfruängen, Jungfruängen, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587393</v>
+        <v>587115</v>
       </c>
       <c r="R16" t="n">
-        <v>6373654</v>
+        <v>6373893</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2403,7 +2367,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2413,7 +2377,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2439,44 +2403,48 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133474318</t>
+          <t>https://artportalen.se/Sighting/133477551</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133471790</v>
+        <v>133477641</v>
       </c>
       <c r="B17" t="n">
-        <v>57162</v>
+        <v>91995</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2485,13 +2453,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>586993</v>
+        <v>587115</v>
       </c>
       <c r="R17" t="n">
-        <v>6373884</v>
+        <v>6373900</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2520,7 +2488,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2530,7 +2498,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2556,59 +2524,65 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133471790</t>
+          <t>https://artportalen.se/Sighting/133477641</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133472286</v>
+        <v>133537484</v>
       </c>
       <c r="B18" t="n">
-        <v>57162</v>
+        <v>91995</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Jungfruängen, Jungfruängen, Sm</t>
+          <t>Ramnebo, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587043</v>
+        <v>586995</v>
       </c>
       <c r="R18" t="n">
-        <v>6373808</v>
+        <v>6373757</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2632,22 +2606,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2656,76 +2630,72 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Ante Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Ante Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133472286</t>
+          <t>https://artportalen.se/Sighting/133537484</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133472844</v>
+        <v>136272895</v>
       </c>
       <c r="B19" t="n">
-        <v>57162</v>
+        <v>92088</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Jungfruängen, Jungfruängen, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587156</v>
+        <v>587110</v>
       </c>
       <c r="R19" t="n">
-        <v>6373777</v>
+        <v>6373857</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2749,22 +2719,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:39</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:39</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2779,65 +2739,72 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133472844</t>
+          <t>https://artportalen.se/Sighting/136272895</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133474359</v>
+        <v>136280972</v>
       </c>
       <c r="B20" t="n">
-        <v>57162</v>
+        <v>92088</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skrabbhagen, Skrabbhagen, Sm</t>
+          <t>Ramnebo Gatgöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>587407</v>
+        <v>587108</v>
       </c>
       <c r="R20" t="n">
-        <v>6373661</v>
+        <v>6373865</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2861,22 +2828,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2885,76 +2852,79 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133474359</t>
+          <t>https://artportalen.se/Sighting/136280972</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133474811</v>
+        <v>136281386</v>
       </c>
       <c r="B21" t="n">
-        <v>57162</v>
+        <v>92088</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skrabbhagen, Skrabbhagen, Sm</t>
+          <t>Ramnebo Gatgöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587449</v>
+        <v>587102</v>
       </c>
       <c r="R21" t="n">
-        <v>6373670</v>
+        <v>6373743</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2978,22 +2948,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3002,76 +2972,75 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133474811</t>
+          <t>https://artportalen.se/Sighting/136281386</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133476774</v>
+        <v>136281160</v>
       </c>
       <c r="B22" t="n">
-        <v>57162</v>
+        <v>80064</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skrabbhagen, Skrabbhagen, Sm</t>
+          <t>Ramnebo Gatgöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587384</v>
+        <v>587413</v>
       </c>
       <c r="R22" t="n">
-        <v>6373702</v>
+        <v>6373685</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3095,22 +3064,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3119,76 +3088,75 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133476774</t>
+          <t>https://artportalen.se/Sighting/136281160</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133477749</v>
+        <v>136281359</v>
       </c>
       <c r="B23" t="n">
-        <v>57162</v>
+        <v>80064</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ramnebo Gatgöl, Ramnebo Gatgöl, Sm</t>
+          <t>Ramnebo Gatgöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587152</v>
+        <v>587219</v>
       </c>
       <c r="R23" t="n">
-        <v>6373902</v>
+        <v>6373714</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3212,27 +3180,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Sandbad?</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3241,81 +3204,75 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133477749</t>
+          <t>https://artportalen.se/Sighting/136281359</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133479929</v>
+        <v>136281412</v>
       </c>
       <c r="B24" t="n">
-        <v>57162</v>
+        <v>80064</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Jungfruängen, Jungfruängen, Sm</t>
+          <t>Ramnebo Gatgöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587112</v>
+        <v>587082</v>
       </c>
       <c r="R24" t="n">
-        <v>6373853</v>
+        <v>6373770</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3339,22 +3296,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3363,33 +3320,34 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133479929</t>
+          <t>https://artportalen.se/Sighting/136281412</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133537533</v>
+        <v>133472246</v>
       </c>
       <c r="B25" t="n">
-        <v>57162</v>
+        <v>57972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3397,53 +3355,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ramnebo, Sm</t>
+          <t>Jungfruängen, Jungfruängen, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587002</v>
+        <v>587043</v>
       </c>
       <c r="R25" t="n">
-        <v>6373747</v>
+        <v>6373808</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3467,22 +3414,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3497,70 +3444,65 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133537533</t>
+          <t>https://artportalen.se/Sighting/133472246</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133472137</v>
+        <v>133474318</v>
       </c>
       <c r="B26" t="n">
-        <v>58136</v>
+        <v>57972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Jungfruängen, Jungfruängen, Sm</t>
+          <t>Kalmarehagen, Kalmarehagen, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587026</v>
+        <v>587393</v>
       </c>
       <c r="R26" t="n">
-        <v>6373851</v>
+        <v>6373654</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3589,7 +3531,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3599,7 +3541,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3625,60 +3567,63 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133472137</t>
+          <t>https://artportalen.se/Sighting/133474318</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133472916</v>
+        <v>136281539</v>
       </c>
       <c r="B27" t="n">
-        <v>58136</v>
+        <v>57980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Jungfruängen, Jungfruängen, Sm</t>
+          <t>Ramnebo Gatgöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587168</v>
+        <v>587129</v>
       </c>
       <c r="R27" t="n">
-        <v>6373780</v>
+        <v>6373844</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3705,22 +3650,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3735,67 +3680,74 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133472916</t>
+          <t>https://artportalen.se/Sighting/136281539</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133475458</v>
+        <v>136281443</v>
       </c>
       <c r="B28" t="n">
-        <v>58136</v>
+        <v>57929</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>100067</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skrabbhagen, Skrabbhagen, Sm</t>
+          <t>Ramnebo Gatgöl, Stora Ramm, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>587556</v>
+        <v>587082</v>
       </c>
       <c r="R28" t="n">
-        <v>6373669</v>
+        <v>6373770</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3822,22 +3774,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Hördes åt nordost mot Ramnebo Gatgöl</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3852,27 +3809,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133475458</t>
+          <t>https://artportalen.se/Sighting/136281443</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133472576</v>
+        <v>133471790</v>
       </c>
       <c r="B29" t="n">
-        <v>58131</v>
+        <v>57162</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3880,37 +3837,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103023</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Jungfruängen, Jungfruängen, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587102</v>
+        <v>586993</v>
       </c>
       <c r="R29" t="n">
-        <v>6373799</v>
+        <v>6373884</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3939,7 +3901,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3949,7 +3911,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3975,7 +3937,1742 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/133471790</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>133472286</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Jungfruängen, Jungfruängen, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>587043</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6373808</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133472286</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>133472844</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Jungfruängen, Jungfruängen, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>587156</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6373777</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133472844</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>133474359</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Skrabbhagen, Skrabbhagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>587407</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6373661</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133474359</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>133474811</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Skrabbhagen, Skrabbhagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>587449</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6373670</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133474811</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>133476774</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Skrabbhagen, Skrabbhagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>587384</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6373702</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133476774</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>133477749</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Ramnebo Gatgöl, Ramnebo Gatgöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>587152</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6373902</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Sandbad?</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133477749</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>133479929</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Jungfruängen, Jungfruängen, Sm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>587112</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6373853</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133479929</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>133537533</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Ramnebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>587002</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6373747</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133537533</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>133472137</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Jungfruängen, Jungfruängen, Sm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>587026</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6373851</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133472137</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>133472916</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Jungfruängen, Jungfruängen, Sm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>587168</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6373780</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133472916</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>133475458</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Skrabbhagen, Skrabbhagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>587556</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6373669</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133475458</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>136274182</v>
+      </c>
+      <c r="B41" t="n">
+        <v>58144</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Jungfruängen, Jungfruängen, Sm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>587217</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6373850</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274182</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>136275420</v>
+      </c>
+      <c r="B42" t="n">
+        <v>58144</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Jungfruängen, Jungfruängen, Sm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>587151</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6373795</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136275420</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>133472576</v>
+      </c>
+      <c r="B43" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Jungfruängen, Jungfruängen, Sm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>587102</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6373799</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/133472576</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>136275005</v>
+      </c>
+      <c r="B44" t="n">
+        <v>56912</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Jungfruängen, Jungfruängen, Sm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>587368</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6373706</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136275005</t>
         </is>
       </c>
     </row>
@@ -4009,6 +5706,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21612-2026 artfynd.xlsx
+++ b/artfynd/A 21612-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136274000</v>
       </c>
       <c r="B2" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>136274843</v>
       </c>
       <c r="B8" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>136281124</v>
       </c>
       <c r="B9" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>136281338</v>
       </c>
       <c r="B10" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>136272895</v>
       </c>
       <c r="B19" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136280972</v>
       </c>
       <c r="B20" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>136281386</v>
       </c>
       <c r="B21" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>136281160</v>
       </c>
       <c r="B22" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>136281359</v>
       </c>
       <c r="B23" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>136281412</v>
       </c>
       <c r="B24" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>136281539</v>
       </c>
       <c r="B27" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>136281443</v>
       </c>
       <c r="B28" t="n">
-        <v>57929</v>
+        <v>57933</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>136274182</v>
       </c>
       <c r="B41" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>136275420</v>
       </c>
       <c r="B42" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>136275005</v>
       </c>
       <c r="B44" t="n">
-        <v>56912</v>
+        <v>56916</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 21612-2026 artfynd.xlsx
+++ b/artfynd/A 21612-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136274000</v>
       </c>
       <c r="B2" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>136274843</v>
       </c>
       <c r="B8" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>136281124</v>
       </c>
       <c r="B9" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>136281338</v>
       </c>
       <c r="B10" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>136272895</v>
       </c>
       <c r="B19" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136280972</v>
       </c>
       <c r="B20" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>136281386</v>
       </c>
       <c r="B21" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>136281160</v>
       </c>
       <c r="B22" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>136281359</v>
       </c>
       <c r="B23" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>136281412</v>
       </c>
       <c r="B24" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>136281539</v>
       </c>
       <c r="B27" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>136281443</v>
       </c>
       <c r="B28" t="n">
-        <v>57933</v>
+        <v>57934</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>136274182</v>
       </c>
       <c r="B41" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>136275420</v>
       </c>
       <c r="B42" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>136275005</v>
       </c>
       <c r="B44" t="n">
-        <v>56916</v>
+        <v>56917</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 21612-2026 artfynd.xlsx
+++ b/artfynd/A 21612-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136274000</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>136274843</v>
       </c>
       <c r="B8" t="n">
-        <v>96888</v>
+        <v>96899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>136281124</v>
       </c>
       <c r="B9" t="n">
-        <v>96888</v>
+        <v>96899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>136281338</v>
       </c>
       <c r="B10" t="n">
-        <v>96888</v>
+        <v>96899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>136272895</v>
       </c>
       <c r="B19" t="n">
-        <v>92095</v>
+        <v>92101</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136280972</v>
       </c>
       <c r="B20" t="n">
-        <v>92095</v>
+        <v>92101</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>136281386</v>
       </c>
       <c r="B21" t="n">
-        <v>92095</v>
+        <v>92101</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>136281160</v>
       </c>
       <c r="B22" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>136281359</v>
       </c>
       <c r="B23" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>136281412</v>
       </c>
       <c r="B24" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 21612-2026 artfynd.xlsx
+++ b/artfynd/A 21612-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136274000</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>136274843</v>
       </c>
       <c r="B8" t="n">
-        <v>96899</v>
+        <v>96912</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>136281124</v>
       </c>
       <c r="B9" t="n">
-        <v>96899</v>
+        <v>96912</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>136281338</v>
       </c>
       <c r="B10" t="n">
-        <v>96899</v>
+        <v>96912</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>136272895</v>
       </c>
       <c r="B19" t="n">
-        <v>92101</v>
+        <v>92108</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136280972</v>
       </c>
       <c r="B20" t="n">
-        <v>92101</v>
+        <v>92108</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>136281386</v>
       </c>
       <c r="B21" t="n">
-        <v>92101</v>
+        <v>92108</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>136281160</v>
       </c>
       <c r="B22" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>136281359</v>
       </c>
       <c r="B23" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>136281412</v>
       </c>
       <c r="B24" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>136281539</v>
       </c>
       <c r="B27" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>136281443</v>
       </c>
       <c r="B28" t="n">
-        <v>57934</v>
+        <v>57939</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>136274182</v>
       </c>
       <c r="B41" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>136275420</v>
       </c>
       <c r="B42" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>136275005</v>
       </c>
       <c r="B44" t="n">
-        <v>56917</v>
+        <v>56922</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 21612-2026 artfynd.xlsx
+++ b/artfynd/A 21612-2026 artfynd.xlsx
@@ -1377,7 +1377,7 @@
         <v>136274843</v>
       </c>
       <c r="B8" t="n">
-        <v>96912</v>
+        <v>96913</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>136281124</v>
       </c>
       <c r="B9" t="n">
-        <v>96912</v>
+        <v>96913</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>136281338</v>
       </c>
       <c r="B10" t="n">
-        <v>96912</v>
+        <v>96913</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>136272895</v>
       </c>
       <c r="B19" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136280972</v>
       </c>
       <c r="B20" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>136281386</v>
       </c>
       <c r="B21" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 21612-2026 artfynd.xlsx
+++ b/artfynd/A 21612-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136274000</v>
       </c>
       <c r="B2" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>136274843</v>
       </c>
       <c r="B8" t="n">
-        <v>96913</v>
+        <v>96926</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>136281124</v>
       </c>
       <c r="B9" t="n">
-        <v>96913</v>
+        <v>96926</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>136281338</v>
       </c>
       <c r="B10" t="n">
-        <v>96913</v>
+        <v>96926</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>136272895</v>
       </c>
       <c r="B19" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136280972</v>
       </c>
       <c r="B20" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>136281386</v>
       </c>
       <c r="B21" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>136281160</v>
       </c>
       <c r="B22" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>136281359</v>
       </c>
       <c r="B23" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>136281412</v>
       </c>
       <c r="B24" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>136281539</v>
       </c>
       <c r="B27" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>136281443</v>
       </c>
       <c r="B28" t="n">
-        <v>57939</v>
+        <v>57952</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>136274182</v>
       </c>
       <c r="B41" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>136275420</v>
       </c>
       <c r="B42" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>136275005</v>
       </c>
       <c r="B44" t="n">
-        <v>56922</v>
+        <v>56935</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 21612-2026 artfynd.xlsx
+++ b/artfynd/A 21612-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136274000</v>
       </c>
       <c r="B2" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>136274843</v>
       </c>
       <c r="B8" t="n">
-        <v>96926</v>
+        <v>96927</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>136281124</v>
       </c>
       <c r="B9" t="n">
-        <v>96926</v>
+        <v>96927</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>136281338</v>
       </c>
       <c r="B10" t="n">
-        <v>96926</v>
+        <v>96927</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>136272895</v>
       </c>
       <c r="B19" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136280972</v>
       </c>
       <c r="B20" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>136281386</v>
       </c>
       <c r="B21" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>136281160</v>
       </c>
       <c r="B22" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>136281359</v>
       </c>
       <c r="B23" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>136281412</v>
       </c>
       <c r="B24" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
